--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e36d409fbc3f23f/Desktop/DLEMBA/(BUS 620) Micro- and Macro-Economic Foundations for Managers/capabilities/marginal-analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richi\AppData\Local\Temp\claude\C--Users-richi-OneDrive-Desktop-DLEMBA--BUS-620--Micro--and-Macro-Economic-Foundations-for-Managers\5b609d10-f30d-4a04-9e9b-01a206f08e8f\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8608342F-831A-4A8E-8E31-C1076339327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F72D68C-3281-4D1C-B1C3-F9468B6636D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="366" yWindow="366" windowWidth="17280" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="172">
   <si>
     <t>Marginal analysis - perfect competition (rebuild 2026-09-04: pooled hourly labor billing)</t>
   </si>
@@ -145,6 +145,9 @@
     <t>hours/week/bed</t>
   </si>
   <si>
+    <t>Case scenario, crop table (carrot: exact fraction, case prints 0.833)</t>
+  </si>
+  <si>
     <t>FERT_COST</t>
   </si>
   <si>
@@ -439,28 +442,34 @@
     <t>NOTES (from spec.md Conventions / Audit findings)</t>
   </si>
   <si>
-    <t>Pooled hourly billing, confirmed with the user 2026-09-04: all three crops' labor hours are pooled;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  the farmer absorbs the first FARMER_HRS_CAP (720) hours at FARMER_RATE; every hour beyond that is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  billed at TEMP_RATE, up to capacity FARMER_HRS_CAP + WORKER_MAX x WORKER_HRS_CAP = 6,480 hours.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  There is no per-worker fixed fee -- MAX_FARMER_COST and MAX_TEMP_WORKER_COST are descriptive only.</t>
-  </si>
-  <si>
-    <t>FARMER_RATE / TEMP_RATE are the UNROUNDED ratios 50000/1440 and 25000/1440 (confirmed), not the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  source table's rounded display figures ($34.72 / $17.36).</t>
-  </si>
-  <si>
-    <t>Rounding is applied at every intermediate step (confirmed): hours to the nearest minute, USD to the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  nearest ten cents -- not only at the final PROFIT figure.</t>
+    <t>Pooled hourly billing: all three crops' labor hours are pooled; the farmer absorbs the first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  FARMER_HRS_CAP (720) hours at FARMER_RATE; every hour beyond that is billed at TEMP_RATE, up to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  capacity FARMER_HRS_CAP + WORKER_MAX x WORKER_HRS_CAP = 6,480 hours. No per-worker fixed fee --</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  MAX_FARMER_COST and MAX_TEMP_WORKER_COST are descriptive only.</t>
+  </si>
+  <si>
+    <t>FARMER_RATE / TEMP_RATE are the UNROUNDED ratios 50000/1440 and 25000/1440, not the source table's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  rounded display figures ($34.72 / $17.36).</t>
+  </si>
+  <si>
+    <t>CAR_HRS is the exact fraction 2.5/3 (0.8333...), not the source table's rounded display figure 0.833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -- see spec.md Audit findings, resolved 2026-09-07: this one input closed the profit check-figure gap.</t>
+  </si>
+  <si>
+    <t>Rounding is applied at every intermediate step: hours to the nearest minute, USD to the nearest ten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cents -- not only at the final PROFIT figure.</t>
   </si>
   <si>
     <t>Check figure: optimal mix is BEDS_TOM=10 / BEDS_CAR=20 / BEDS_MES=30, stated profit $42,762 within $5.</t>
@@ -469,28 +478,25 @@
     <t xml:space="preserve">  Full enumeration over the whole feasible grid (0-20/0-20/0-30, sum&lt;=64, labor&lt;=6,480 hrs) confirms</t>
   </si>
   <si>
-    <t xml:space="preserve">  10/20/30 IS the exact global profit-maximizing allocation under this formula. Computed profit here</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  is $42,768.30 -- a $6.30 gap outside the stated +/-$5. Every rate/rounding variant tried lands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  $6-13 above the stated figure, never inside the band, so the bed allocation is treated as the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  confirmed acceptance criterion and the profit gap is flagged (see spec.md Audit findings) rather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  than silently absorbed.</t>
-  </si>
-  <si>
-    <t>Standalone MC=Price crossings (spec check figure: 10, 10, 6) could not be reproduced under any single</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  consistent per-crop costing convention -- see the 'Standalone Diagnostics' sheet for the two</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  readings tried (all-farmer-rate and all-temp-rate) side by side.</t>
+    <t xml:space="preserve">  10/20/30 IS the exact global profit-maximizing allocation. Computed profit is $42,761.70 with this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  workbook's rounding ($42,761.66 with none) -- inside the +/-$5 band.</t>
+  </si>
+  <si>
+    <t>Standalone MC=Price crossings (spec check figure: 10, 10, 6): the Standalone Diagnostics sheet applies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  the same farmer-first tiered billing to each crop's own private schedule and reads the crossing as</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  the FIRST bed where marginal cost exceeds price (the standard textbook stopping rule) -- this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  reproduces 10, 10, 6 exactly. See spec.md Audit findings for why the LAST bed with MC&lt;=price (the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  economically rigorous answer once MC stops being monotonic) instead gives 10, 20, 30.</t>
   </si>
   <si>
     <t>Decision cells hold the profit-maximising integer allocation found by full enumeration; the embedded</t>
@@ -499,10 +505,10 @@
     <t xml:space="preserve">  Solver model (Data &gt; Solver) reproduces it.</t>
   </si>
   <si>
-    <t>Standalone (single-crop, unconstrained) marginal-cost = price diagnostics</t>
-  </si>
-  <si>
-    <t>Spec check figure: crossings at 10, 10, 6 beds (tomato, carrot, mesclun), within one bed. Neither reading below reproduces all three -- see Model sheet Notes.</t>
+    <t>Standalone (single-crop, farmer-first-tiered) marginal-cost = price diagnostics</t>
+  </si>
+  <si>
+    <t>Each crop gets its own private 720-hr farmer allocation, then TEMP_RATE overflow -- same billing as the Model sheet, applied standalone. Crossing = first bed where MC &gt; PRICE (matches spec check figure 10, 10, 6 exactly). See spec.md Audit findings for why this differs from the LAST bed with MC&lt;=price (10, 20, 30) once MC stops being monotonic.</t>
   </si>
   <si>
     <t>TOMATOES</t>
@@ -514,19 +520,16 @@
     <t>LABOR_HRS(q)</t>
   </si>
   <si>
-    <t>COST @ FARMER_RATE</t>
-  </si>
-  <si>
-    <t>MC @ FARMER_RATE</t>
-  </si>
-  <si>
-    <t>COST @ TEMP_RATE</t>
-  </si>
-  <si>
-    <t>MC @ TEMP_RATE</t>
-  </si>
-  <si>
-    <t>Crossing (last q with MC&lt;=PRICE)</t>
+    <t>TIERED COST(q)</t>
+  </si>
+  <si>
+    <t>MC(q)</t>
+  </si>
+  <si>
+    <t>RUNNING MAX MC</t>
+  </si>
+  <si>
+    <t>Crossing: first bed where MC &gt; PRICE (i.e. last bed still on the plan)</t>
   </si>
   <si>
     <t>CARROTS</t>
@@ -613,7 +616,7 @@
     <t xml:space="preserve">  PROFIT</t>
   </si>
   <si>
-    <t>$42,768.30  (spec check figure: $42,762 within $5 -- see Audit findings in spec.md)</t>
+    <t>$42,761.70  (spec check figure: $42,762 within $5 -- matches; see Audit findings in spec.md)</t>
   </si>
 </sst>
 </file>
@@ -729,7 +732,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -762,11 +765,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -1079,7 +1081,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.7" x14ac:dyDescent="0.6">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="27"/>
@@ -1090,7 +1092,7 @@
       <c r="G1" s="27"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="27"/>
@@ -1101,7 +1103,7 @@
       <c r="G2" s="27"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="27"/>
@@ -1159,7 +1161,8 @@
         <v>2.5</v>
       </c>
       <c r="C7" s="7">
-        <v>0.83299999999999996</v>
+        <f>2.5/3</f>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D7" s="7">
         <v>1.25</v>
@@ -1168,12 +1171,12 @@
         <v>13</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="4">
         <v>880</v>
@@ -1193,7 +1196,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="8">
         <v>0.1</v>
@@ -1205,7 +1208,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>11</v>
@@ -1213,7 +1216,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="9">
         <v>20</v>
@@ -1225,15 +1228,15 @@
         <v>30</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="29" t="s">
-        <v>19</v>
+      <c r="A12" s="28" t="s">
+        <v>20</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="27"/>
@@ -1247,7 +1250,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>7</v>
@@ -1258,149 +1261,149 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="9">
         <v>36</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="4">
         <v>20000</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="10">
         <v>720</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="4">
         <v>24998</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="11">
         <f>50000/1440</f>
         <v>34.722222222222221</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="10">
         <v>1440</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="4">
         <v>25000</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="11">
         <f>25000/1440</f>
         <v>17.361111111111111</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="9">
         <v>4</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="9">
         <v>64</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="29" t="s">
-        <v>46</v>
+      <c r="A25" s="28" t="s">
+        <v>47</v>
       </c>
       <c r="B25" s="27"/>
       <c r="C25" s="27"/>
@@ -1426,12 +1429,12 @@
         <v>7</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="12">
         <v>10</v>
@@ -1443,27 +1446,27 @@
         <v>30</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" s="14">
         <f>BEDS_TOM+BEDS_CAR+BEDS_MES</f>
         <v>60</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="29" t="s">
-        <v>51</v>
+      <c r="A30" s="28" t="s">
+        <v>52</v>
       </c>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -1486,15 +1489,15 @@
         <v>6</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32" s="15">
         <f>ROUND(BEDS_TOM*TOM_HRS*WEEKS*(1+TOM_DIM_PCT)^BEDS_TOM*60,0)/60</f>
@@ -1502,7 +1505,7 @@
       </c>
       <c r="C32" s="15">
         <f>ROUND(BEDS_CAR*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^BEDS_CAR*60,0)/60</f>
-        <v>982.7833333333333</v>
+        <v>983.16666666666663</v>
       </c>
       <c r="D32" s="15">
         <f>ROUND(BEDS_MES*MES_HRS*WEEKS*(1+MES_DIM_PCT)^BEDS_MES*60,0)/60</f>
@@ -1510,15 +1513,15 @@
       </c>
       <c r="E32" s="16">
         <f>SUM(B32:D32)</f>
-        <v>5276.8333333333339</v>
+        <v>5277.2166666666672</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="29" t="s">
-        <v>56</v>
+      <c r="A34" s="28" t="s">
+        <v>57</v>
       </c>
       <c r="B34" s="27"/>
       <c r="C34" s="27"/>
@@ -1532,108 +1535,108 @@
         <v>3</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" s="15">
         <f>MIN(LABOR_HRS_TOTAL,FARMER_HRS_CAP)</f>
         <v>720</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B37" s="15">
         <f>MAX(0,LABOR_HRS_TOTAL-FARMER_HRS_CAP)</f>
-        <v>4556.8333333333339</v>
+        <v>4557.2166666666672</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B38" s="17">
         <f>ROUND(FARMER_HRS_USED*FARMER_RATE,1)</f>
         <v>25000</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B39" s="17">
         <f>ROUND(EXCESS_HRS*TEMP_RATE,1)</f>
-        <v>79111.7</v>
+        <v>79118.3</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B40" s="17">
         <f>FARMER_COST+TEMP_COST</f>
-        <v>104111.7</v>
+        <v>104118.3</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B41" s="18">
         <f>IF(EXCESS_HRS&lt;=0,0,ROUNDUP(EXCESS_HRS/WORKER_HRS_CAP,0))</f>
         <v>4</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="29" t="s">
-        <v>71</v>
+      <c r="A43" s="28" t="s">
+        <v>72</v>
       </c>
       <c r="B43" s="27"/>
       <c r="C43" s="27"/>
@@ -1656,15 +1659,15 @@
         <v>6</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B45" s="19">
         <f>BEDS_TOM*TOM_PRICE</f>
@@ -1683,12 +1686,12 @@
         <v>210880</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B46" s="19">
         <f>BEDS_TOM*TOM_FERT_COST</f>
@@ -1707,42 +1710,42 @@
         <v>44000</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B47" s="21">
         <f>ROUND(FIXED_COST+FERT_COST+LABOR_COST,1)</f>
-        <v>168111.7</v>
+        <v>168118.3</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B48" s="21">
         <f>ROUND(TOTAL_REVENUE-TOTAL_COST,1)</f>
-        <v>42768.3</v>
+        <v>42761.7</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="29" t="s">
-        <v>80</v>
+      <c r="A50" s="28" t="s">
+        <v>81</v>
       </c>
       <c r="B50" s="27"/>
       <c r="C50" s="27"/>
@@ -1753,126 +1756,126 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B52" s="22" t="b">
         <f>BEDS_PLANTED&lt;=BEDS_TOTAL</f>
         <v>1</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B53" s="22" t="b">
         <f>BEDS_TOM&lt;=TOM_MAXBED</f>
         <v>1</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B54" s="22" t="b">
         <f>BEDS_CAR&lt;=CAR_MAXBED</f>
         <v>1</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B55" s="22" t="b">
         <f>BEDS_MES&lt;=MES_MAXBED</f>
         <v>1</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B56" s="22" t="b">
         <f>LABOR_HRS_TOTAL&lt;=(FARMER_HRS_CAP+WORKER_MAX*WORKER_HRS_CAP)</f>
         <v>1</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B57" s="22" t="b">
         <f>N_WORKERS_NEEDED&lt;=WORKER_MAX</f>
         <v>1</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B58" s="22" t="b">
         <f>AND(BEDS_TOM=INT(BEDS_TOM),BEDS_CAR=INT(BEDS_CAR),BEDS_MES=INT(BEDS_MES))</f>
         <v>1</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B59" s="22" t="b">
         <f>ABS((TOTAL_REVENUE-FIXED_COST-FERT_COST-LABOR_COST)-PROFIT)&lt;0.005</f>
         <v>1</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B60" s="23" t="b">
         <f>AND(B52:B59)</f>
         <v>1</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="29" t="s">
-        <v>102</v>
+      <c r="A62" s="28" t="s">
+        <v>103</v>
       </c>
       <c r="B62" s="27"/>
       <c r="C62" s="27"/>
@@ -1886,7 +1889,7 @@
         <v>3</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>7</v>
@@ -1894,103 +1897,103 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B64" s="18">
         <f>BEDS_TOM</f>
         <v>10</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B65" s="18">
         <f>BEDS_CAR</f>
         <v>20</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B66" s="18">
         <f>BEDS_MES</f>
         <v>30</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B67" s="18">
         <f>N_WORKERS_NEEDED</f>
         <v>4</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B68" s="17">
         <f>FARMER_COST</f>
         <v>25000</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B69" s="17">
         <f>TEMP_COST</f>
-        <v>79111.7</v>
+        <v>79118.3</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B70" s="19">
         <f>TOTAL_REVENUE</f>
         <v>210880</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B71" s="21">
         <f>PROFIT</f>
-        <v>42768.3</v>
+        <v>42761.7</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="29" t="s">
-        <v>111</v>
+      <c r="A74" s="28" t="s">
+        <v>112</v>
       </c>
       <c r="B74" s="27"/>
       <c r="C74" s="27"/>
@@ -2000,8 +2003,8 @@
       <c r="G74" s="27"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="28" t="s">
-        <v>112</v>
+      <c r="A75" s="26" t="s">
+        <v>113</v>
       </c>
       <c r="B75" s="27"/>
       <c r="C75" s="27"/>
@@ -2011,8 +2014,8 @@
       <c r="G75" s="27"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="28" t="s">
-        <v>113</v>
+      <c r="A76" s="26" t="s">
+        <v>114</v>
       </c>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
@@ -2022,8 +2025,8 @@
       <c r="G76" s="27"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="28" t="s">
-        <v>114</v>
+      <c r="A77" s="26" t="s">
+        <v>115</v>
       </c>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
@@ -2033,8 +2036,8 @@
       <c r="G77" s="27"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="28" t="s">
-        <v>115</v>
+      <c r="A78" s="26" t="s">
+        <v>116</v>
       </c>
       <c r="B78" s="27"/>
       <c r="C78" s="27"/>
@@ -2044,8 +2047,8 @@
       <c r="G78" s="27"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="28" t="s">
-        <v>116</v>
+      <c r="A79" s="26" t="s">
+        <v>117</v>
       </c>
       <c r="B79" s="27"/>
       <c r="C79" s="27"/>
@@ -2055,8 +2058,8 @@
       <c r="G79" s="27"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="28" t="s">
-        <v>117</v>
+      <c r="A80" s="26" t="s">
+        <v>118</v>
       </c>
       <c r="B80" s="27"/>
       <c r="C80" s="27"/>
@@ -2066,8 +2069,8 @@
       <c r="G80" s="27"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="28" t="s">
-        <v>118</v>
+      <c r="A81" s="26" t="s">
+        <v>119</v>
       </c>
       <c r="B81" s="27"/>
       <c r="C81" s="27"/>
@@ -2077,8 +2080,8 @@
       <c r="G81" s="27"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="28" t="s">
-        <v>119</v>
+      <c r="A82" s="26" t="s">
+        <v>120</v>
       </c>
       <c r="B82" s="27"/>
       <c r="C82" s="27"/>
@@ -2088,8 +2091,8 @@
       <c r="G82" s="27"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="28" t="s">
-        <v>120</v>
+      <c r="A83" s="26" t="s">
+        <v>121</v>
       </c>
       <c r="B83" s="27"/>
       <c r="C83" s="27"/>
@@ -2099,8 +2102,8 @@
       <c r="G83" s="27"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="28" t="s">
-        <v>121</v>
+      <c r="A84" s="26" t="s">
+        <v>122</v>
       </c>
       <c r="B84" s="27"/>
       <c r="C84" s="27"/>
@@ -2110,8 +2113,8 @@
       <c r="G84" s="27"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="28" t="s">
-        <v>122</v>
+      <c r="A85" s="26" t="s">
+        <v>123</v>
       </c>
       <c r="B85" s="27"/>
       <c r="C85" s="27"/>
@@ -2121,8 +2124,8 @@
       <c r="G85" s="27"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="28" t="s">
-        <v>123</v>
+      <c r="A86" s="26" t="s">
+        <v>124</v>
       </c>
       <c r="B86" s="27"/>
       <c r="C86" s="27"/>
@@ -2132,8 +2135,8 @@
       <c r="G86" s="27"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="28" t="s">
-        <v>124</v>
+      <c r="A87" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="B87" s="27"/>
       <c r="C87" s="27"/>
@@ -2143,8 +2146,8 @@
       <c r="G87" s="27"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="28" t="s">
-        <v>125</v>
+      <c r="A88" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="B88" s="27"/>
       <c r="C88" s="27"/>
@@ -2154,8 +2157,8 @@
       <c r="G88" s="27"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="28" t="s">
-        <v>126</v>
+      <c r="A89" s="26" t="s">
+        <v>127</v>
       </c>
       <c r="B89" s="27"/>
       <c r="C89" s="27"/>
@@ -2165,8 +2168,8 @@
       <c r="G89" s="27"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="28" t="s">
-        <v>127</v>
+      <c r="A90" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="B90" s="27"/>
       <c r="C90" s="27"/>
@@ -2176,8 +2179,8 @@
       <c r="G90" s="27"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="28" t="s">
-        <v>128</v>
+      <c r="A91" s="26" t="s">
+        <v>129</v>
       </c>
       <c r="B91" s="27"/>
       <c r="C91" s="27"/>
@@ -2187,8 +2190,8 @@
       <c r="G91" s="27"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="28" t="s">
-        <v>129</v>
+      <c r="A92" s="26" t="s">
+        <v>130</v>
       </c>
       <c r="B92" s="27"/>
       <c r="C92" s="27"/>
@@ -2198,8 +2201,8 @@
       <c r="G92" s="27"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="28" t="s">
-        <v>130</v>
+      <c r="A93" s="26" t="s">
+        <v>131</v>
       </c>
       <c r="B93" s="27"/>
       <c r="C93" s="27"/>
@@ -2209,8 +2212,8 @@
       <c r="G93" s="27"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="28" t="s">
-        <v>131</v>
+      <c r="A94" s="26" t="s">
+        <v>132</v>
       </c>
       <c r="B94" s="27"/>
       <c r="C94" s="27"/>
@@ -2219,23 +2222,24 @@
       <c r="F94" s="27"/>
       <c r="G94" s="27"/>
     </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B95" s="27"/>
+      <c r="C95" s="27"/>
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
+      <c r="F95" s="27"/>
+      <c r="G95" s="27"/>
+    </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A93:G93"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A83:G83"/>
-    <mergeCell ref="A92:G92"/>
-    <mergeCell ref="A82:G82"/>
+  <mergeCells count="32">
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A86:G86"/>
     <mergeCell ref="A76:G76"/>
     <mergeCell ref="A85:G85"/>
-    <mergeCell ref="A91:G91"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A88:G88"/>
     <mergeCell ref="A94:G94"/>
@@ -2251,10 +2255,20 @@
     <mergeCell ref="A80:G80"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A93:G93"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="A91:G91"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A30:G30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2269,8 +2283,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.7" x14ac:dyDescent="0.6">
-      <c r="A1" s="26" t="s">
-        <v>132</v>
+      <c r="A1" s="29" t="s">
+        <v>134</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -2280,8 +2294,8 @@
       <c r="G1" s="27"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="28" t="s">
-        <v>133</v>
+      <c r="A2" s="26" t="s">
+        <v>135</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -2291,8 +2305,8 @@
       <c r="G2" s="27"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="29" t="s">
-        <v>134</v>
+      <c r="A4" s="28" t="s">
+        <v>136</v>
       </c>
       <c r="B4" s="27"/>
       <c r="C4" s="27"/>
@@ -2303,23 +2317,21 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>140</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2331,17 +2343,14 @@
         <v>0</v>
       </c>
       <c r="C6" s="17">
-        <f t="shared" ref="C6:C26" si="1">ROUND(B6*FARMER_RATE+A6*TOM_FERT_COST,1)</f>
+        <f t="shared" ref="C6:C26" si="1">ROUND(IF(B6&lt;=FARMER_HRS_CAP,B6*FARMER_RATE,FARMER_HRS_CAP*FARMER_RATE+(B6-FARMER_HRS_CAP)*TEMP_RATE)+A6*TOM_FERT_COST,1)</f>
         <v>0</v>
       </c>
       <c r="D6" s="17">
         <v>0</v>
       </c>
       <c r="E6" s="17">
-        <f t="shared" ref="E6:E26" si="2">ROUND(B6*TEMP_RATE+A6*TOM_FERT_COST,1)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="17">
+        <f>MAX($D$6:D6)</f>
         <v>0</v>
       </c>
     </row>
@@ -2358,16 +2367,12 @@
         <v>4317.5</v>
       </c>
       <c r="D7" s="17">
-        <f t="shared" ref="D7:D26" si="3">C7-C6</f>
+        <f t="shared" ref="D7:D26" si="2">C7-C6</f>
         <v>4317.5</v>
       </c>
       <c r="E7" s="17">
-        <f t="shared" si="2"/>
-        <v>2598.8000000000002</v>
-      </c>
-      <c r="F7" s="17">
-        <f t="shared" ref="F7:F26" si="4">E7-E6</f>
-        <v>2598.8000000000002</v>
+        <f>MAX($D$6:D7)</f>
+        <v>4317.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2383,16 +2388,12 @@
         <v>9322.5</v>
       </c>
       <c r="D8" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5005</v>
       </c>
       <c r="E8" s="17">
-        <f t="shared" si="2"/>
-        <v>5541.3</v>
-      </c>
-      <c r="F8" s="17">
-        <f t="shared" si="4"/>
-        <v>2942.5</v>
+        <f>MAX($D$6:D8)</f>
+        <v>5005</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2408,16 +2409,12 @@
         <v>15118</v>
       </c>
       <c r="D9" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5795.5</v>
       </c>
       <c r="E9" s="17">
-        <f t="shared" si="2"/>
-        <v>8879</v>
-      </c>
-      <c r="F9" s="17">
-        <f t="shared" si="4"/>
-        <v>3337.7</v>
+        <f>MAX($D$6:D9)</f>
+        <v>5795.5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2433,16 +2430,12 @@
         <v>21821.5</v>
       </c>
       <c r="D10" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6703.5</v>
       </c>
       <c r="E10" s="17">
-        <f t="shared" si="2"/>
-        <v>12670.8</v>
-      </c>
-      <c r="F10" s="17">
-        <f t="shared" si="4"/>
-        <v>3791.7999999999993</v>
+        <f>MAX($D$6:D10)</f>
+        <v>6703.5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2455,19 +2448,15 @@
       </c>
       <c r="C11" s="17">
         <f t="shared" si="1"/>
-        <v>29564.400000000001</v>
+        <v>29482.2</v>
       </c>
       <c r="D11" s="17">
-        <f t="shared" si="3"/>
-        <v>7742.9000000000015</v>
+        <f t="shared" si="2"/>
+        <v>7660.7000000000007</v>
       </c>
       <c r="E11" s="17">
-        <f t="shared" si="2"/>
-        <v>16982.2</v>
-      </c>
-      <c r="F11" s="17">
-        <f t="shared" si="4"/>
-        <v>4311.4000000000015</v>
+        <f>MAX($D$6:D11)</f>
+        <v>7660.7000000000007</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2480,19 +2469,15 @@
       </c>
       <c r="C12" s="17">
         <f t="shared" si="1"/>
-        <v>38497</v>
+        <v>34388.5</v>
       </c>
       <c r="D12" s="17">
-        <f t="shared" si="3"/>
-        <v>8932.5999999999985</v>
+        <f t="shared" si="2"/>
+        <v>4906.2999999999993</v>
       </c>
       <c r="E12" s="17">
-        <f t="shared" si="2"/>
-        <v>21888.5</v>
-      </c>
-      <c r="F12" s="17">
-        <f t="shared" si="4"/>
-        <v>4906.2999999999993</v>
+        <f>MAX($D$6:D12)</f>
+        <v>7660.7000000000007</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2505,19 +2490,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="1"/>
-        <v>48788.5</v>
+        <v>39974.199999999997</v>
       </c>
       <c r="D13" s="17">
-        <f t="shared" si="3"/>
-        <v>10291.5</v>
+        <f t="shared" si="2"/>
+        <v>5585.6999999999971</v>
       </c>
       <c r="E13" s="17">
-        <f t="shared" si="2"/>
-        <v>27474.2</v>
-      </c>
-      <c r="F13" s="17">
-        <f t="shared" si="4"/>
-        <v>5585.7000000000007</v>
+        <f>MAX($D$6:D13)</f>
+        <v>7660.7000000000007</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2530,19 +2511,15 @@
       </c>
       <c r="C14" s="17">
         <f t="shared" si="1"/>
-        <v>60629.7</v>
+        <v>46334.8</v>
       </c>
       <c r="D14" s="17">
-        <f t="shared" si="3"/>
-        <v>11841.199999999997</v>
+        <f t="shared" si="2"/>
+        <v>6360.6000000000058</v>
       </c>
       <c r="E14" s="17">
-        <f t="shared" si="2"/>
-        <v>33834.800000000003</v>
-      </c>
-      <c r="F14" s="17">
-        <f t="shared" si="4"/>
-        <v>6360.6000000000022</v>
+        <f>MAX($D$6:D14)</f>
+        <v>7660.7000000000007</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2555,19 +2532,15 @@
       </c>
       <c r="C15" s="17">
         <f t="shared" si="1"/>
-        <v>74237.100000000006</v>
+        <v>53578.6</v>
       </c>
       <c r="D15" s="17">
-        <f t="shared" si="3"/>
-        <v>13607.400000000009</v>
+        <f t="shared" si="2"/>
+        <v>7243.7999999999956</v>
       </c>
       <c r="E15" s="17">
-        <f t="shared" si="2"/>
-        <v>41078.6</v>
-      </c>
-      <c r="F15" s="17">
-        <f t="shared" si="4"/>
-        <v>7243.7999999999956</v>
+        <f>MAX($D$6:D15)</f>
+        <v>7660.7000000000007</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2580,18 +2553,14 @@
       </c>
       <c r="C16" s="17">
         <f t="shared" si="1"/>
-        <v>89854.399999999994</v>
+        <v>61827.199999999997</v>
       </c>
       <c r="D16" s="17">
-        <f t="shared" si="3"/>
-        <v>15617.299999999988</v>
+        <f t="shared" si="2"/>
+        <v>8248.5999999999985</v>
       </c>
       <c r="E16" s="17">
-        <f t="shared" si="2"/>
-        <v>49327.199999999997</v>
-      </c>
-      <c r="F16" s="17">
-        <f t="shared" si="4"/>
+        <f>MAX($D$6:D16)</f>
         <v>8248.5999999999985</v>
       </c>
     </row>
@@ -2605,19 +2574,15 @@
       </c>
       <c r="C17" s="17">
         <f t="shared" si="1"/>
-        <v>107755.8</v>
+        <v>71217.899999999994</v>
       </c>
       <c r="D17" s="17">
-        <f t="shared" si="3"/>
-        <v>17901.400000000009</v>
+        <f t="shared" si="2"/>
+        <v>9390.6999999999971</v>
       </c>
       <c r="E17" s="17">
-        <f t="shared" si="2"/>
-        <v>58717.9</v>
-      </c>
-      <c r="F17" s="17">
-        <f t="shared" si="4"/>
-        <v>9390.7000000000044</v>
+        <f>MAX($D$6:D17)</f>
+        <v>9390.6999999999971</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2630,19 +2595,15 @@
       </c>
       <c r="C18" s="17">
         <f t="shared" si="1"/>
-        <v>128251</v>
+        <v>81905.5</v>
       </c>
       <c r="D18" s="17">
-        <f t="shared" si="3"/>
-        <v>20495.199999999997</v>
+        <f t="shared" si="2"/>
+        <v>10687.600000000006</v>
       </c>
       <c r="E18" s="17">
-        <f t="shared" si="2"/>
-        <v>69405.5</v>
-      </c>
-      <c r="F18" s="17">
-        <f t="shared" si="4"/>
-        <v>10687.599999999999</v>
+        <f>MAX($D$6:D18)</f>
+        <v>10687.600000000006</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2655,18 +2616,14 @@
       </c>
       <c r="C19" s="17">
         <f t="shared" si="1"/>
-        <v>151688.29999999999</v>
+        <v>94064.1</v>
       </c>
       <c r="D19" s="17">
-        <f t="shared" si="3"/>
-        <v>23437.299999999988</v>
+        <f t="shared" si="2"/>
+        <v>12158.600000000006</v>
       </c>
       <c r="E19" s="17">
-        <f t="shared" si="2"/>
-        <v>81564.100000000006</v>
-      </c>
-      <c r="F19" s="17">
-        <f t="shared" si="4"/>
+        <f>MAX($D$6:D19)</f>
         <v>12158.600000000006</v>
       </c>
     </row>
@@ -2680,18 +2637,14 @@
       </c>
       <c r="C20" s="17">
         <f t="shared" si="1"/>
-        <v>178460.6</v>
+        <v>107890.3</v>
       </c>
       <c r="D20" s="17">
-        <f t="shared" si="3"/>
-        <v>26772.300000000017</v>
+        <f t="shared" si="2"/>
+        <v>13826.199999999997</v>
       </c>
       <c r="E20" s="17">
-        <f t="shared" si="2"/>
-        <v>95390.3</v>
-      </c>
-      <c r="F20" s="17">
-        <f t="shared" si="4"/>
+        <f>MAX($D$6:D20)</f>
         <v>13826.199999999997</v>
       </c>
     </row>
@@ -2705,18 +2658,14 @@
       </c>
       <c r="C21" s="17">
         <f t="shared" si="1"/>
-        <v>209008.4</v>
+        <v>123604.2</v>
       </c>
       <c r="D21" s="17">
-        <f t="shared" si="3"/>
-        <v>30547.799999999988</v>
+        <f t="shared" si="2"/>
+        <v>15713.899999999994</v>
       </c>
       <c r="E21" s="17">
-        <f t="shared" si="2"/>
-        <v>111104.2</v>
-      </c>
-      <c r="F21" s="17">
-        <f t="shared" si="4"/>
+        <f>MAX($D$6:D21)</f>
         <v>15713.899999999994</v>
       </c>
     </row>
@@ -2730,18 +2679,14 @@
       </c>
       <c r="C22" s="17">
         <f t="shared" si="1"/>
-        <v>243828.8</v>
+        <v>141454.39999999999</v>
       </c>
       <c r="D22" s="17">
-        <f t="shared" si="3"/>
-        <v>34820.399999999994</v>
+        <f t="shared" si="2"/>
+        <v>17850.199999999997</v>
       </c>
       <c r="E22" s="17">
-        <f t="shared" si="2"/>
-        <v>128954.4</v>
-      </c>
-      <c r="F22" s="17">
-        <f t="shared" si="4"/>
+        <f>MAX($D$6:D22)</f>
         <v>17850.199999999997</v>
       </c>
     </row>
@@ -2755,18 +2700,14 @@
       </c>
       <c r="C23" s="17">
         <f t="shared" si="1"/>
-        <v>283478.5</v>
+        <v>161719.29999999999</v>
       </c>
       <c r="D23" s="17">
-        <f t="shared" si="3"/>
-        <v>39649.700000000012</v>
+        <f t="shared" si="2"/>
+        <v>20264.899999999994</v>
       </c>
       <c r="E23" s="17">
-        <f t="shared" si="2"/>
-        <v>149219.29999999999</v>
-      </c>
-      <c r="F23" s="17">
-        <f t="shared" si="4"/>
+        <f>MAX($D$6:D23)</f>
         <v>20264.899999999994</v>
       </c>
     </row>
@@ -2780,18 +2721,14 @@
       </c>
       <c r="C24" s="17">
         <f t="shared" si="1"/>
-        <v>328585.40000000002</v>
+        <v>184712.7</v>
       </c>
       <c r="D24" s="17">
-        <f t="shared" si="3"/>
-        <v>45106.900000000023</v>
+        <f t="shared" si="2"/>
+        <v>22993.400000000023</v>
       </c>
       <c r="E24" s="17">
-        <f t="shared" si="2"/>
-        <v>172212.7</v>
-      </c>
-      <c r="F24" s="17">
-        <f t="shared" si="4"/>
+        <f>MAX($D$6:D24)</f>
         <v>22993.400000000023</v>
       </c>
     </row>
@@ -2805,18 +2742,14 @@
       </c>
       <c r="C25" s="17">
         <f t="shared" si="1"/>
-        <v>379851.9</v>
+        <v>210786</v>
       </c>
       <c r="D25" s="17">
-        <f t="shared" si="3"/>
-        <v>51266.5</v>
+        <f t="shared" si="2"/>
+        <v>26073.299999999988</v>
       </c>
       <c r="E25" s="17">
-        <f t="shared" si="2"/>
-        <v>198286</v>
-      </c>
-      <c r="F25" s="17">
-        <f t="shared" si="4"/>
+        <f>MAX($D$6:D25)</f>
         <v>26073.299999999988</v>
       </c>
     </row>
@@ -2830,37 +2763,29 @@
       </c>
       <c r="C26" s="17">
         <f t="shared" si="1"/>
-        <v>438068.8</v>
+        <v>240334.4</v>
       </c>
       <c r="D26" s="17">
-        <f t="shared" si="3"/>
-        <v>58216.899999999965</v>
+        <f t="shared" si="2"/>
+        <v>29548.399999999994</v>
       </c>
       <c r="E26" s="17">
-        <f t="shared" si="2"/>
-        <v>227834.4</v>
-      </c>
-      <c r="F26" s="17">
-        <f t="shared" si="4"/>
+        <f>MAX($D$6:D26)</f>
         <v>29548.399999999994</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="30" t="s">
-        <v>141</v>
+      <c r="A27" s="24" t="s">
+        <v>142</v>
       </c>
       <c r="D27" s="25">
-        <f>SUMPRODUCT(MAX((D6:D26&lt;=TOM_PRICE)*A6:A26))</f>
-        <v>5</v>
-      </c>
-      <c r="F27" s="25">
-        <f>SUMPRODUCT(MAX((F6:F26&lt;=TOM_PRICE)*A6:A26))</f>
+        <f>SUMPRODUCT((E6:E26&lt;=TOM_PRICE)*1)-1</f>
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="29" t="s">
-        <v>142</v>
+      <c r="A29" s="28" t="s">
+        <v>143</v>
       </c>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
@@ -2871,23 +2796,21 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>140</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2895,21 +2818,18 @@
         <v>0</v>
       </c>
       <c r="B31" s="15">
-        <f t="shared" ref="B31:B51" si="5">ROUND(A31*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A31*60,0)/60</f>
+        <f t="shared" ref="B31:B51" si="3">ROUND(A31*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A31*60,0)/60</f>
         <v>0</v>
       </c>
       <c r="C31" s="17">
-        <f t="shared" ref="C31:C51" si="6">ROUND(B31*FARMER_RATE+A31*CAR_FERT_COST,1)</f>
+        <f t="shared" ref="C31:C51" si="4">ROUND(IF(B31&lt;=FARMER_HRS_CAP,B31*FARMER_RATE,FARMER_HRS_CAP*FARMER_RATE+(B31-FARMER_HRS_CAP)*TEMP_RATE)+A31*CAR_FERT_COST,1)</f>
         <v>0</v>
       </c>
       <c r="D31" s="17">
         <v>0</v>
       </c>
       <c r="E31" s="17">
-        <f t="shared" ref="E31:E51" si="7">ROUND(B31*TEMP_RATE+A31*CAR_FERT_COST,1)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="17">
+        <f>MAX($D$31:D31)</f>
         <v>0</v>
       </c>
     </row>
@@ -2918,424 +2838,356 @@
         <v>1</v>
       </c>
       <c r="B32" s="15">
-        <f t="shared" si="5"/>
-        <v>30.733333333333334</v>
+        <f t="shared" si="3"/>
+        <v>30.75</v>
       </c>
       <c r="C32" s="17">
-        <f t="shared" si="6"/>
-        <v>1507.1</v>
+        <f t="shared" si="4"/>
+        <v>1507.7</v>
       </c>
       <c r="D32" s="17">
-        <f t="shared" ref="D32:D51" si="8">C32-C31</f>
-        <v>1507.1</v>
+        <f t="shared" ref="D32:D51" si="5">C32-C31</f>
+        <v>1507.7</v>
       </c>
       <c r="E32" s="17">
-        <f t="shared" si="7"/>
-        <v>973.6</v>
-      </c>
-      <c r="F32" s="17">
-        <f t="shared" ref="F32:F51" si="9">E32-E31</f>
-        <v>973.6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D32)</f>
+        <v>1507.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="5">
         <v>2</v>
       </c>
       <c r="B33" s="15">
+        <f t="shared" si="3"/>
+        <v>63.033333333333331</v>
+      </c>
+      <c r="C33" s="17">
+        <f t="shared" si="4"/>
+        <v>3068.7</v>
+      </c>
+      <c r="D33" s="17">
         <f t="shared" si="5"/>
-        <v>63.016666666666666</v>
-      </c>
-      <c r="C33" s="17">
-        <f t="shared" si="6"/>
-        <v>3068.1</v>
-      </c>
-      <c r="D33" s="17">
-        <f t="shared" si="8"/>
-        <v>1561</v>
+        <v>1560.9999999999998</v>
       </c>
       <c r="E33" s="17">
-        <f t="shared" si="7"/>
-        <v>1974</v>
-      </c>
-      <c r="F33" s="17">
-        <f t="shared" si="9"/>
-        <v>1000.4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D33)</f>
+        <v>1560.9999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="5">
         <v>3</v>
       </c>
       <c r="B34" s="15">
+        <f t="shared" si="3"/>
+        <v>96.916666666666671</v>
+      </c>
+      <c r="C34" s="17">
+        <f t="shared" si="4"/>
+        <v>4685.2</v>
+      </c>
+      <c r="D34" s="17">
         <f t="shared" si="5"/>
-        <v>96.88333333333334</v>
-      </c>
-      <c r="C34" s="17">
-        <f t="shared" si="6"/>
-        <v>4684</v>
-      </c>
-      <c r="D34" s="17">
-        <f t="shared" si="8"/>
-        <v>1615.9</v>
+        <v>1616.5</v>
       </c>
       <c r="E34" s="17">
-        <f t="shared" si="7"/>
-        <v>3002</v>
-      </c>
-      <c r="F34" s="17">
-        <f t="shared" si="9"/>
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D34)</f>
+        <v>1616.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="5">
         <v>4</v>
       </c>
       <c r="B35" s="15">
+        <f t="shared" si="3"/>
+        <v>132.44999999999999</v>
+      </c>
+      <c r="C35" s="17">
+        <f t="shared" si="4"/>
+        <v>6359</v>
+      </c>
+      <c r="D35" s="17">
         <f t="shared" si="5"/>
-        <v>132.4</v>
-      </c>
-      <c r="C35" s="17">
-        <f t="shared" si="6"/>
-        <v>6357.2</v>
-      </c>
-      <c r="D35" s="17">
-        <f t="shared" si="8"/>
-        <v>1673.1999999999998</v>
+        <v>1673.8000000000002</v>
       </c>
       <c r="E35" s="17">
-        <f t="shared" si="7"/>
-        <v>4058.6</v>
-      </c>
-      <c r="F35" s="17">
-        <f t="shared" si="9"/>
-        <v>1056.5999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D35)</f>
+        <v>1673.8000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="5">
         <v>5</v>
       </c>
       <c r="B36" s="15">
+        <f t="shared" si="3"/>
+        <v>169.71666666666667</v>
+      </c>
+      <c r="C36" s="17">
+        <f t="shared" si="4"/>
+        <v>8092.9</v>
+      </c>
+      <c r="D36" s="17">
         <f t="shared" si="5"/>
-        <v>169.65</v>
-      </c>
-      <c r="C36" s="17">
-        <f t="shared" si="6"/>
-        <v>8090.6</v>
-      </c>
-      <c r="D36" s="17">
-        <f t="shared" si="8"/>
-        <v>1733.4000000000005</v>
+        <v>1733.8999999999996</v>
       </c>
       <c r="E36" s="17">
-        <f t="shared" si="7"/>
-        <v>5145.3</v>
-      </c>
-      <c r="F36" s="17">
-        <f t="shared" si="9"/>
-        <v>1086.7000000000003</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D36)</f>
+        <v>1733.8999999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="5">
         <v>6</v>
       </c>
       <c r="B37" s="15">
+        <f t="shared" si="3"/>
+        <v>208.75</v>
+      </c>
+      <c r="C37" s="17">
+        <f t="shared" si="4"/>
+        <v>9888.2999999999993</v>
+      </c>
+      <c r="D37" s="17">
         <f t="shared" si="5"/>
-        <v>208.66666666666666</v>
-      </c>
-      <c r="C37" s="17">
-        <f t="shared" si="6"/>
-        <v>9885.4</v>
-      </c>
-      <c r="D37" s="17">
-        <f t="shared" si="8"/>
-        <v>1794.7999999999993</v>
+        <v>1795.3999999999996</v>
       </c>
       <c r="E37" s="17">
-        <f t="shared" si="7"/>
-        <v>6262.7</v>
-      </c>
-      <c r="F37" s="17">
-        <f t="shared" si="9"/>
-        <v>1117.3999999999996</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D37)</f>
+        <v>1795.3999999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="5">
         <v>7</v>
       </c>
       <c r="B38" s="15">
+        <f t="shared" si="3"/>
+        <v>249.61666666666667</v>
+      </c>
+      <c r="C38" s="17">
+        <f t="shared" si="4"/>
+        <v>11747.2</v>
+      </c>
+      <c r="D38" s="17">
         <f t="shared" si="5"/>
-        <v>249.51666666666668</v>
-      </c>
-      <c r="C38" s="17">
-        <f t="shared" si="6"/>
-        <v>11743.8</v>
-      </c>
-      <c r="D38" s="17">
-        <f t="shared" si="8"/>
-        <v>1858.3999999999996</v>
+        <v>1858.9000000000015</v>
       </c>
       <c r="E38" s="17">
-        <f t="shared" si="7"/>
-        <v>7411.9</v>
-      </c>
-      <c r="F38" s="17">
-        <f t="shared" si="9"/>
-        <v>1149.1999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D38)</f>
+        <v>1858.9000000000015</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="5">
         <v>8</v>
       </c>
       <c r="B39" s="15">
+        <f t="shared" si="3"/>
+        <v>292.41666666666669</v>
+      </c>
+      <c r="C39" s="17">
+        <f t="shared" si="4"/>
+        <v>13673.4</v>
+      </c>
+      <c r="D39" s="17">
         <f t="shared" si="5"/>
-        <v>292.3</v>
-      </c>
-      <c r="C39" s="17">
-        <f t="shared" si="6"/>
-        <v>13669.3</v>
-      </c>
-      <c r="D39" s="17">
-        <f t="shared" si="8"/>
-        <v>1925.5</v>
+        <v>1926.1999999999989</v>
       </c>
       <c r="E39" s="17">
-        <f t="shared" si="7"/>
-        <v>8594.7000000000007</v>
-      </c>
-      <c r="F39" s="17">
-        <f t="shared" si="9"/>
-        <v>1182.8000000000011</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D39)</f>
+        <v>1926.1999999999989</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="5">
         <v>9</v>
       </c>
       <c r="B40" s="15">
+        <f t="shared" si="3"/>
+        <v>337.2</v>
+      </c>
+      <c r="C40" s="17">
+        <f t="shared" si="4"/>
+        <v>15668.3</v>
+      </c>
+      <c r="D40" s="17">
         <f t="shared" si="5"/>
-        <v>337.05</v>
-      </c>
-      <c r="C40" s="17">
-        <f t="shared" si="6"/>
-        <v>15663.1</v>
-      </c>
-      <c r="D40" s="17">
-        <f t="shared" si="8"/>
-        <v>1993.8000000000011</v>
+        <v>1994.8999999999996</v>
       </c>
       <c r="E40" s="17">
-        <f t="shared" si="7"/>
-        <v>9811.6</v>
-      </c>
-      <c r="F40" s="17">
-        <f t="shared" si="9"/>
-        <v>1216.8999999999996</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D40)</f>
+        <v>1994.8999999999996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="5">
         <v>10</v>
       </c>
       <c r="B41" s="15">
+        <f t="shared" si="3"/>
+        <v>384.03333333333336</v>
+      </c>
+      <c r="C41" s="17">
+        <f t="shared" si="4"/>
+        <v>17734.5</v>
+      </c>
+      <c r="D41" s="17">
         <f t="shared" si="5"/>
-        <v>383.86666666666667</v>
-      </c>
-      <c r="C41" s="17">
-        <f t="shared" si="6"/>
-        <v>17728.7</v>
-      </c>
-      <c r="D41" s="17">
-        <f t="shared" si="8"/>
-        <v>2065.6000000000004</v>
+        <v>2066.2000000000007</v>
       </c>
       <c r="E41" s="17">
-        <f t="shared" si="7"/>
-        <v>11064.4</v>
-      </c>
-      <c r="F41" s="17">
-        <f t="shared" si="9"/>
-        <v>1252.7999999999993</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D41)</f>
+        <v>2066.2000000000007</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="5">
         <v>11</v>
       </c>
       <c r="B42" s="15">
+        <f t="shared" si="3"/>
+        <v>432.98333333333335</v>
+      </c>
+      <c r="C42" s="17">
+        <f t="shared" si="4"/>
+        <v>19874.099999999999</v>
+      </c>
+      <c r="D42" s="17">
         <f t="shared" si="5"/>
-        <v>432.81666666666666</v>
-      </c>
-      <c r="C42" s="17">
-        <f t="shared" si="6"/>
-        <v>19868.400000000001</v>
-      </c>
-      <c r="D42" s="17">
-        <f t="shared" si="8"/>
-        <v>2139.7000000000007</v>
+        <v>2139.5999999999985</v>
       </c>
       <c r="E42" s="17">
-        <f t="shared" si="7"/>
-        <v>12354.2</v>
-      </c>
-      <c r="F42" s="17">
-        <f t="shared" si="9"/>
-        <v>1289.8000000000011</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D42)</f>
+        <v>2139.5999999999985</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="5">
         <v>12</v>
       </c>
       <c r="B43" s="15">
+        <f t="shared" si="3"/>
+        <v>484.16666666666669</v>
+      </c>
+      <c r="C43" s="17">
+        <f t="shared" si="4"/>
+        <v>22091.3</v>
+      </c>
+      <c r="D43" s="17">
         <f t="shared" si="5"/>
-        <v>483.96666666666664</v>
-      </c>
-      <c r="C43" s="17">
-        <f t="shared" si="6"/>
-        <v>22084.400000000001</v>
-      </c>
-      <c r="D43" s="17">
-        <f t="shared" si="8"/>
-        <v>2216</v>
+        <v>2217.2000000000007</v>
       </c>
       <c r="E43" s="17">
-        <f t="shared" si="7"/>
-        <v>13682.2</v>
-      </c>
-      <c r="F43" s="17">
-        <f t="shared" si="9"/>
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D43)</f>
+        <v>2217.2000000000007</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="5">
         <v>13</v>
       </c>
       <c r="B44" s="15">
+        <f t="shared" si="3"/>
+        <v>537.61666666666667</v>
+      </c>
+      <c r="C44" s="17">
+        <f t="shared" si="4"/>
+        <v>24387.200000000001</v>
+      </c>
+      <c r="D44" s="17">
         <f t="shared" si="5"/>
-        <v>537.4</v>
-      </c>
-      <c r="C44" s="17">
-        <f t="shared" si="6"/>
-        <v>24379.7</v>
-      </c>
-      <c r="D44" s="17">
-        <f t="shared" si="8"/>
-        <v>2295.2999999999993</v>
+        <v>2295.9000000000015</v>
       </c>
       <c r="E44" s="17">
-        <f t="shared" si="7"/>
-        <v>15049.9</v>
-      </c>
-      <c r="F44" s="17">
-        <f t="shared" si="9"/>
-        <v>1367.6999999999989</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D44)</f>
+        <v>2295.9000000000015</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="5">
         <v>14</v>
       </c>
       <c r="B45" s="15">
+        <f t="shared" si="3"/>
+        <v>593.45000000000005</v>
+      </c>
+      <c r="C45" s="17">
+        <f t="shared" si="4"/>
+        <v>26765.9</v>
+      </c>
+      <c r="D45" s="17">
         <f t="shared" si="5"/>
-        <v>593.2166666666667</v>
-      </c>
-      <c r="C45" s="17">
-        <f t="shared" si="6"/>
-        <v>26757.8</v>
-      </c>
-      <c r="D45" s="17">
-        <f t="shared" si="8"/>
-        <v>2378.0999999999985</v>
+        <v>2378.7000000000007</v>
       </c>
       <c r="E45" s="17">
-        <f t="shared" si="7"/>
-        <v>16458.900000000001</v>
-      </c>
-      <c r="F45" s="17">
-        <f t="shared" si="9"/>
-        <v>1409.0000000000018</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D45)</f>
+        <v>2378.7000000000007</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="5">
         <v>15</v>
       </c>
       <c r="B46" s="15">
+        <f t="shared" si="3"/>
+        <v>651.73333333333335</v>
+      </c>
+      <c r="C46" s="17">
+        <f t="shared" si="4"/>
+        <v>29229.599999999999</v>
+      </c>
+      <c r="D46" s="17">
         <f t="shared" si="5"/>
-        <v>651.4666666666667</v>
-      </c>
-      <c r="C46" s="17">
-        <f t="shared" si="6"/>
-        <v>29220.400000000001</v>
-      </c>
-      <c r="D46" s="17">
-        <f t="shared" si="8"/>
-        <v>2462.6000000000022</v>
+        <v>2463.6999999999971</v>
       </c>
       <c r="E46" s="17">
-        <f t="shared" si="7"/>
-        <v>17910.2</v>
-      </c>
-      <c r="F46" s="17">
-        <f t="shared" si="9"/>
-        <v>1451.2999999999993</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D46)</f>
+        <v>2463.6999999999971</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="5">
         <v>16</v>
       </c>
       <c r="B47" s="15">
+        <f t="shared" si="3"/>
+        <v>712.56666666666672</v>
+      </c>
+      <c r="C47" s="17">
+        <f t="shared" si="4"/>
+        <v>31781.9</v>
+      </c>
+      <c r="D47" s="17">
         <f t="shared" si="5"/>
-        <v>712.2833333333333</v>
-      </c>
-      <c r="C47" s="17">
-        <f t="shared" si="6"/>
-        <v>31772.1</v>
-      </c>
-      <c r="D47" s="17">
-        <f t="shared" si="8"/>
-        <v>2551.6999999999971</v>
+        <v>2552.3000000000029</v>
       </c>
       <c r="E47" s="17">
-        <f t="shared" si="7"/>
-        <v>19406</v>
-      </c>
-      <c r="F47" s="17">
-        <f t="shared" si="9"/>
-        <v>1495.7999999999993</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$31:D47)</f>
+        <v>2552.3000000000029</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="5">
         <v>17</v>
       </c>
       <c r="B48" s="15">
+        <f t="shared" si="3"/>
+        <v>776.0333333333333</v>
+      </c>
+      <c r="C48" s="17">
+        <f t="shared" si="4"/>
+        <v>33452.800000000003</v>
+      </c>
+      <c r="D48" s="17">
         <f t="shared" si="5"/>
-        <v>775.7166666666667</v>
-      </c>
-      <c r="C48" s="17">
-        <f t="shared" si="6"/>
-        <v>34414.6</v>
-      </c>
-      <c r="D48" s="17">
-        <f t="shared" si="8"/>
-        <v>2642.5</v>
+        <v>1670.9000000000015</v>
       </c>
       <c r="E48" s="17">
-        <f t="shared" si="7"/>
-        <v>20947.3</v>
-      </c>
-      <c r="F48" s="17">
-        <f t="shared" si="9"/>
-        <v>1541.2999999999993</v>
+        <f>MAX($D$31:D48)</f>
+        <v>2552.3000000000029</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3343,24 +3195,20 @@
         <v>18</v>
       </c>
       <c r="B49" s="15">
+        <f t="shared" si="3"/>
+        <v>842.2166666666667</v>
+      </c>
+      <c r="C49" s="17">
+        <f t="shared" si="4"/>
+        <v>35041.800000000003</v>
+      </c>
+      <c r="D49" s="17">
         <f t="shared" si="5"/>
-        <v>841.88333333333333</v>
-      </c>
-      <c r="C49" s="17">
-        <f t="shared" si="6"/>
-        <v>37152.1</v>
-      </c>
-      <c r="D49" s="17">
-        <f t="shared" si="8"/>
-        <v>2737.5</v>
+        <v>1589</v>
       </c>
       <c r="E49" s="17">
-        <f t="shared" si="7"/>
-        <v>22536</v>
-      </c>
-      <c r="F49" s="17">
-        <f t="shared" si="9"/>
-        <v>1588.7000000000007</v>
+        <f>MAX($D$31:D49)</f>
+        <v>2552.3000000000029</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3368,24 +3216,20 @@
         <v>19</v>
       </c>
       <c r="B50" s="15">
+        <f t="shared" si="3"/>
+        <v>911.23333333333335</v>
+      </c>
+      <c r="C50" s="17">
+        <f t="shared" si="4"/>
+        <v>36680</v>
+      </c>
+      <c r="D50" s="17">
         <f t="shared" si="5"/>
-        <v>910.86666666666667</v>
-      </c>
-      <c r="C50" s="17">
-        <f t="shared" si="6"/>
-        <v>39987.300000000003</v>
-      </c>
-      <c r="D50" s="17">
-        <f t="shared" si="8"/>
-        <v>2835.2000000000044</v>
+        <v>1638.1999999999971</v>
       </c>
       <c r="E50" s="17">
-        <f t="shared" si="7"/>
-        <v>24173.7</v>
-      </c>
-      <c r="F50" s="17">
-        <f t="shared" si="9"/>
-        <v>1637.7000000000007</v>
+        <f>MAX($D$31:D50)</f>
+        <v>2552.3000000000029</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3393,42 +3237,34 @@
         <v>20</v>
       </c>
       <c r="B51" s="15">
+        <f t="shared" si="3"/>
+        <v>983.16666666666663</v>
+      </c>
+      <c r="C51" s="17">
+        <f t="shared" si="4"/>
+        <v>38368.9</v>
+      </c>
+      <c r="D51" s="17">
         <f t="shared" si="5"/>
-        <v>982.7833333333333</v>
-      </c>
-      <c r="C51" s="17">
-        <f t="shared" si="6"/>
-        <v>42924.4</v>
-      </c>
-      <c r="D51" s="17">
-        <f t="shared" si="8"/>
-        <v>2937.0999999999985</v>
+        <v>1688.9000000000015</v>
       </c>
       <c r="E51" s="17">
-        <f t="shared" si="7"/>
-        <v>25862.2</v>
-      </c>
-      <c r="F51" s="17">
-        <f t="shared" si="9"/>
-        <v>1688.5</v>
+        <f>MAX($D$31:D51)</f>
+        <v>2552.3000000000029</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="30" t="s">
-        <v>141</v>
+      <c r="A52" s="24" t="s">
+        <v>142</v>
       </c>
       <c r="D52" s="25">
-        <f>SUMPRODUCT(MAX((D31:D51&lt;=CAR_PRICE)*A31:A51))</f>
+        <f>SUMPRODUCT((E31:E51&lt;=CAR_PRICE)*1)-1</f>
         <v>10</v>
       </c>
-      <c r="F52" s="25">
-        <f>SUMPRODUCT(MAX((F31:F51&lt;=CAR_PRICE)*A31:A51))</f>
-        <v>20</v>
-      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="29" t="s">
-        <v>143</v>
+      <c r="A54" s="28" t="s">
+        <v>144</v>
       </c>
       <c r="B54" s="27"/>
       <c r="C54" s="27"/>
@@ -3439,23 +3275,21 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>140</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3463,21 +3297,18 @@
         <v>0</v>
       </c>
       <c r="B56" s="15">
-        <f t="shared" ref="B56:B86" si="10">ROUND(A56*MES_HRS*WEEKS*(1+MES_DIM_PCT)^A56*60,0)/60</f>
+        <f t="shared" ref="B56:B86" si="6">ROUND(A56*MES_HRS*WEEKS*(1+MES_DIM_PCT)^A56*60,0)/60</f>
         <v>0</v>
       </c>
       <c r="C56" s="17">
-        <f t="shared" ref="C56:C86" si="11">ROUND(B56*FARMER_RATE+A56*MES_FERT_COST,1)</f>
+        <f t="shared" ref="C56:C86" si="7">ROUND(IF(B56&lt;=FARMER_HRS_CAP,B56*FARMER_RATE,FARMER_HRS_CAP*FARMER_RATE+(B56-FARMER_HRS_CAP)*TEMP_RATE)+A56*MES_FERT_COST,1)</f>
         <v>0</v>
       </c>
       <c r="D56" s="17">
         <v>0</v>
       </c>
       <c r="E56" s="17">
-        <f t="shared" ref="E56:E86" si="12">ROUND(B56*TEMP_RATE+A56*MES_FERT_COST,1)</f>
-        <v>0</v>
-      </c>
-      <c r="F56" s="17">
+        <f>MAX($D$56:D56)</f>
         <v>0</v>
       </c>
     </row>
@@ -3486,24 +3317,20 @@
         <v>1</v>
       </c>
       <c r="B57" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>45.56666666666667</v>
       </c>
       <c r="C57" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>2462.1999999999998</v>
       </c>
       <c r="D57" s="17">
-        <f t="shared" ref="D57:D86" si="13">C57-C56</f>
+        <f t="shared" ref="D57:D86" si="8">C57-C56</f>
         <v>2462.1999999999998</v>
       </c>
       <c r="E57" s="17">
-        <f t="shared" si="12"/>
-        <v>1671.1</v>
-      </c>
-      <c r="F57" s="17">
-        <f t="shared" ref="F57:F86" si="14">E57-E56</f>
-        <v>1671.1</v>
+        <f>MAX($D$56:D57)</f>
+        <v>2462.1999999999998</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3511,24 +3338,20 @@
         <v>2</v>
       </c>
       <c r="B58" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>92.266666666666666</v>
       </c>
       <c r="C58" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>4963.7</v>
       </c>
       <c r="D58" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2501.5</v>
       </c>
       <c r="E58" s="17">
-        <f t="shared" si="12"/>
-        <v>3361.9</v>
-      </c>
-      <c r="F58" s="17">
-        <f t="shared" si="14"/>
-        <v>1690.8000000000002</v>
+        <f>MAX($D$56:D58)</f>
+        <v>2501.5</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3536,24 +3359,20 @@
         <v>3</v>
       </c>
       <c r="B59" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>140.13333333333333</v>
       </c>
       <c r="C59" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>7505.7</v>
       </c>
       <c r="D59" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2542</v>
       </c>
       <c r="E59" s="17">
-        <f t="shared" si="12"/>
-        <v>5072.8999999999996</v>
-      </c>
-      <c r="F59" s="17">
-        <f t="shared" si="14"/>
-        <v>1710.9999999999995</v>
+        <f>MAX($D$56:D59)</f>
+        <v>2542</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3561,24 +3380,20 @@
         <v>4</v>
       </c>
       <c r="B60" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>189.16666666666666</v>
       </c>
       <c r="C60" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>10088.299999999999</v>
       </c>
       <c r="D60" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2582.5999999999995</v>
       </c>
       <c r="E60" s="17">
-        <f t="shared" si="12"/>
-        <v>6804.1</v>
-      </c>
-      <c r="F60" s="17">
-        <f t="shared" si="14"/>
-        <v>1731.2000000000007</v>
+        <f>MAX($D$56:D60)</f>
+        <v>2582.5999999999995</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3586,24 +3401,20 @@
         <v>5</v>
       </c>
       <c r="B61" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>239.41666666666666</v>
       </c>
       <c r="C61" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>12713.1</v>
       </c>
       <c r="D61" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2624.8000000000011</v>
       </c>
       <c r="E61" s="17">
-        <f t="shared" si="12"/>
-        <v>8556.5</v>
-      </c>
-      <c r="F61" s="17">
-        <f t="shared" si="14"/>
-        <v>1752.3999999999996</v>
+        <f>MAX($D$56:D61)</f>
+        <v>2624.8000000000011</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3611,24 +3422,20 @@
         <v>6</v>
       </c>
       <c r="B62" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>290.89999999999998</v>
       </c>
       <c r="C62" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>15380.7</v>
       </c>
       <c r="D62" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2667.6000000000004</v>
       </c>
       <c r="E62" s="17">
-        <f t="shared" si="12"/>
-        <v>10330.299999999999</v>
-      </c>
-      <c r="F62" s="17">
-        <f t="shared" si="14"/>
-        <v>1773.7999999999993</v>
+        <f>MAX($D$56:D62)</f>
+        <v>2667.6000000000004</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3636,24 +3443,20 @@
         <v>7</v>
       </c>
       <c r="B63" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>343.61666666666667</v>
       </c>
       <c r="C63" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>18091.099999999999</v>
       </c>
       <c r="D63" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2710.3999999999978</v>
       </c>
       <c r="E63" s="17">
-        <f t="shared" si="12"/>
-        <v>12125.6</v>
-      </c>
-      <c r="F63" s="17">
-        <f t="shared" si="14"/>
-        <v>1795.3000000000011</v>
+        <f>MAX($D$56:D63)</f>
+        <v>2710.3999999999978</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3661,599 +3464,500 @@
         <v>8</v>
       </c>
       <c r="B64" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>397.61666666666667</v>
       </c>
       <c r="C64" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>20846.099999999999</v>
       </c>
       <c r="D64" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2755</v>
       </c>
       <c r="E64" s="17">
-        <f t="shared" si="12"/>
-        <v>13943.1</v>
-      </c>
-      <c r="F64" s="17">
-        <f t="shared" si="14"/>
-        <v>1817.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D64)</f>
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="5">
         <v>9</v>
       </c>
       <c r="B65" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>452.9</v>
       </c>
       <c r="C65" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>23645.7</v>
       </c>
       <c r="D65" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2799.6000000000022</v>
       </c>
       <c r="E65" s="17">
-        <f t="shared" si="12"/>
-        <v>15782.8</v>
-      </c>
-      <c r="F65" s="17">
-        <f t="shared" si="14"/>
-        <v>1839.6999999999989</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D65)</f>
+        <v>2799.6000000000022</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="5">
         <v>10</v>
       </c>
       <c r="B66" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>509.51666666666665</v>
       </c>
       <c r="C66" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>26491.599999999999</v>
       </c>
       <c r="D66" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2845.8999999999978</v>
       </c>
       <c r="E66" s="17">
-        <f t="shared" si="12"/>
-        <v>17645.8</v>
-      </c>
-      <c r="F66" s="17">
-        <f t="shared" si="14"/>
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D66)</f>
+        <v>2845.8999999999978</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="5">
         <v>11</v>
       </c>
       <c r="B67" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>567.48333333333335</v>
       </c>
       <c r="C67" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>29384.3</v>
       </c>
       <c r="D67" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2892.7000000000007</v>
       </c>
       <c r="E67" s="17">
-        <f t="shared" si="12"/>
-        <v>19532.099999999999</v>
-      </c>
-      <c r="F67" s="17">
-        <f t="shared" si="14"/>
-        <v>1886.2999999999993</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D67)</f>
+        <v>2892.7000000000007</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="5">
         <v>12</v>
       </c>
       <c r="B68" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>626.79999999999995</v>
       </c>
       <c r="C68" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>32323.9</v>
       </c>
       <c r="D68" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2939.6000000000022</v>
       </c>
       <c r="E68" s="17">
-        <f t="shared" si="12"/>
-        <v>21441.9</v>
-      </c>
-      <c r="F68" s="17">
-        <f t="shared" si="14"/>
-        <v>1909.8000000000029</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D68)</f>
+        <v>2939.6000000000022</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="5">
         <v>13</v>
       </c>
       <c r="B69" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>687.5333333333333</v>
       </c>
       <c r="C69" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>35312.699999999997</v>
       </c>
       <c r="D69" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>2988.7999999999956</v>
       </c>
       <c r="E69" s="17">
-        <f t="shared" si="12"/>
-        <v>23376.3</v>
-      </c>
-      <c r="F69" s="17">
-        <f t="shared" si="14"/>
-        <v>1934.3999999999978</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D69)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="5">
         <v>14</v>
       </c>
       <c r="B70" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>749.66666666666663</v>
       </c>
       <c r="C70" s="17">
-        <f t="shared" si="11"/>
-        <v>38350.1</v>
+        <f t="shared" si="7"/>
+        <v>37835</v>
       </c>
       <c r="D70" s="17">
-        <f t="shared" si="13"/>
-        <v>3037.4000000000015</v>
+        <f t="shared" si="8"/>
+        <v>2522.3000000000029</v>
       </c>
       <c r="E70" s="17">
-        <f t="shared" si="12"/>
-        <v>25335</v>
-      </c>
-      <c r="F70" s="17">
-        <f t="shared" si="14"/>
-        <v>1958.7000000000007</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D70)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="5">
         <v>15</v>
       </c>
       <c r="B71" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>813.26666666666665</v>
       </c>
       <c r="C71" s="17">
-        <f t="shared" si="11"/>
-        <v>41438.400000000001</v>
+        <f t="shared" si="7"/>
+        <v>39819.199999999997</v>
       </c>
       <c r="D71" s="17">
-        <f t="shared" si="13"/>
-        <v>3088.3000000000029</v>
+        <f t="shared" si="8"/>
+        <v>1984.1999999999971</v>
       </c>
       <c r="E71" s="17">
-        <f t="shared" si="12"/>
-        <v>27319.200000000001</v>
-      </c>
-      <c r="F71" s="17">
-        <f t="shared" si="14"/>
-        <v>1984.2000000000007</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D71)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="5">
         <v>16</v>
       </c>
       <c r="B72" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>878.31666666666672</v>
       </c>
       <c r="C72" s="17">
-        <f t="shared" si="11"/>
-        <v>44577.1</v>
+        <f t="shared" si="7"/>
+        <v>41828.6</v>
       </c>
       <c r="D72" s="17">
-        <f t="shared" si="13"/>
-        <v>3138.6999999999971</v>
+        <f t="shared" si="8"/>
+        <v>2009.4000000000015</v>
       </c>
       <c r="E72" s="17">
-        <f t="shared" si="12"/>
-        <v>29328.6</v>
-      </c>
-      <c r="F72" s="17">
-        <f t="shared" si="14"/>
-        <v>2009.3999999999978</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D72)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="5">
         <v>17</v>
       </c>
       <c r="B73" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>944.88333333333333</v>
       </c>
       <c r="C73" s="17">
-        <f t="shared" si="11"/>
-        <v>47768.4</v>
+        <f t="shared" si="7"/>
+        <v>43864.2</v>
       </c>
       <c r="D73" s="17">
-        <f t="shared" si="13"/>
-        <v>3191.3000000000029</v>
+        <f t="shared" si="8"/>
+        <v>2035.5999999999985</v>
       </c>
       <c r="E73" s="17">
-        <f t="shared" si="12"/>
-        <v>31364.2</v>
-      </c>
-      <c r="F73" s="17">
-        <f t="shared" si="14"/>
-        <v>2035.6000000000022</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D73)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="5">
         <v>18</v>
       </c>
       <c r="B74" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1012.9666666666667</v>
       </c>
       <c r="C74" s="17">
-        <f t="shared" si="11"/>
-        <v>51012.5</v>
+        <f t="shared" si="7"/>
+        <v>45926.2</v>
       </c>
       <c r="D74" s="17">
-        <f t="shared" si="13"/>
-        <v>3244.0999999999985</v>
+        <f t="shared" si="8"/>
+        <v>2062</v>
       </c>
       <c r="E74" s="17">
-        <f t="shared" si="12"/>
-        <v>33426.199999999997</v>
-      </c>
-      <c r="F74" s="17">
-        <f t="shared" si="14"/>
-        <v>2061.9999999999964</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D74)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="5">
         <v>19</v>
       </c>
       <c r="B75" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1082.6166666666666</v>
       </c>
       <c r="C75" s="17">
-        <f t="shared" si="11"/>
-        <v>54310.9</v>
+        <f t="shared" si="7"/>
+        <v>48015.4</v>
       </c>
       <c r="D75" s="17">
-        <f t="shared" si="13"/>
-        <v>3298.4000000000015</v>
+        <f t="shared" si="8"/>
+        <v>2089.2000000000044</v>
       </c>
       <c r="E75" s="17">
-        <f t="shared" si="12"/>
-        <v>35515.4</v>
-      </c>
-      <c r="F75" s="17">
-        <f t="shared" si="14"/>
-        <v>2089.2000000000044</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D75)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="5">
         <v>20</v>
       </c>
       <c r="B76" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1153.8333333333333</v>
       </c>
       <c r="C76" s="17">
-        <f t="shared" si="11"/>
-        <v>57663.7</v>
+        <f t="shared" si="7"/>
+        <v>50131.8</v>
       </c>
       <c r="D76" s="17">
-        <f t="shared" si="13"/>
-        <v>3352.7999999999956</v>
+        <f t="shared" si="8"/>
+        <v>2116.4000000000015</v>
       </c>
       <c r="E76" s="17">
-        <f t="shared" si="12"/>
-        <v>37631.800000000003</v>
-      </c>
-      <c r="F76" s="17">
-        <f t="shared" si="14"/>
-        <v>2116.4000000000015</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D76)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="5">
         <v>21</v>
       </c>
       <c r="B77" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1226.6666666666667</v>
       </c>
       <c r="C77" s="17">
-        <f t="shared" si="11"/>
-        <v>61072.6</v>
+        <f t="shared" si="7"/>
+        <v>52276.3</v>
       </c>
       <c r="D77" s="17">
-        <f t="shared" si="13"/>
-        <v>3408.9000000000015</v>
+        <f t="shared" si="8"/>
+        <v>2144.5</v>
       </c>
       <c r="E77" s="17">
-        <f t="shared" si="12"/>
-        <v>39776.300000000003</v>
-      </c>
-      <c r="F77" s="17">
-        <f t="shared" si="14"/>
-        <v>2144.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D77)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="5">
         <v>22</v>
       </c>
       <c r="B78" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1301.1500000000001</v>
       </c>
       <c r="C78" s="17">
-        <f t="shared" si="11"/>
-        <v>64538.8</v>
+        <f t="shared" si="7"/>
+        <v>54449.4</v>
       </c>
       <c r="D78" s="17">
-        <f t="shared" si="13"/>
-        <v>3466.2000000000044</v>
+        <f t="shared" si="8"/>
+        <v>2173.0999999999985</v>
       </c>
       <c r="E78" s="17">
-        <f t="shared" si="12"/>
-        <v>41949.4</v>
-      </c>
-      <c r="F78" s="17">
-        <f t="shared" si="14"/>
-        <v>2173.0999999999985</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D78)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="5">
         <v>23</v>
       </c>
       <c r="B79" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1377.3</v>
       </c>
       <c r="C79" s="17">
-        <f t="shared" si="11"/>
-        <v>68062.899999999994</v>
+        <f t="shared" si="7"/>
+        <v>56651.5</v>
       </c>
       <c r="D79" s="17">
-        <f t="shared" si="13"/>
-        <v>3524.0999999999913</v>
+        <f t="shared" si="8"/>
+        <v>2202.0999999999985</v>
       </c>
       <c r="E79" s="17">
-        <f t="shared" si="12"/>
-        <v>44151.5</v>
-      </c>
-      <c r="F79" s="17">
-        <f t="shared" si="14"/>
-        <v>2202.0999999999985</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D79)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="5">
         <v>24</v>
       </c>
       <c r="B80" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1455.1333333333334</v>
       </c>
       <c r="C80" s="17">
-        <f t="shared" si="11"/>
-        <v>71645.5</v>
+        <f t="shared" si="7"/>
+        <v>58882.7</v>
       </c>
       <c r="D80" s="17">
-        <f t="shared" si="13"/>
-        <v>3582.6000000000058</v>
+        <f t="shared" si="8"/>
+        <v>2231.1999999999971</v>
       </c>
       <c r="E80" s="17">
-        <f t="shared" si="12"/>
-        <v>46382.7</v>
-      </c>
-      <c r="F80" s="17">
-        <f t="shared" si="14"/>
-        <v>2231.1999999999971</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D80)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="5">
         <v>25</v>
       </c>
       <c r="B81" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1534.7166666666667</v>
       </c>
       <c r="C81" s="17">
-        <f t="shared" si="11"/>
-        <v>75288.800000000003</v>
+        <f t="shared" si="7"/>
+        <v>61144.4</v>
       </c>
       <c r="D81" s="17">
-        <f t="shared" si="13"/>
-        <v>3643.3000000000029</v>
+        <f t="shared" si="8"/>
+        <v>2261.7000000000044</v>
       </c>
       <c r="E81" s="17">
-        <f t="shared" si="12"/>
-        <v>48644.4</v>
-      </c>
-      <c r="F81" s="17">
-        <f t="shared" si="14"/>
-        <v>2261.7000000000044</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D81)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="5">
         <v>26</v>
       </c>
       <c r="B82" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1616.05</v>
       </c>
       <c r="C82" s="17">
-        <f t="shared" si="11"/>
-        <v>78992.800000000003</v>
+        <f t="shared" si="7"/>
+        <v>63436.4</v>
       </c>
       <c r="D82" s="17">
-        <f t="shared" si="13"/>
-        <v>3704</v>
+        <f t="shared" si="8"/>
+        <v>2292</v>
       </c>
       <c r="E82" s="17">
-        <f t="shared" si="12"/>
-        <v>50936.4</v>
-      </c>
-      <c r="F82" s="17">
-        <f t="shared" si="14"/>
-        <v>2292</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D82)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="5">
         <v>27</v>
       </c>
       <c r="B83" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1699.1833333333334</v>
       </c>
       <c r="C83" s="17">
-        <f t="shared" si="11"/>
-        <v>82759.399999999994</v>
+        <f t="shared" si="7"/>
+        <v>65759.7</v>
       </c>
       <c r="D83" s="17">
-        <f t="shared" si="13"/>
-        <v>3766.5999999999913</v>
+        <f t="shared" si="8"/>
+        <v>2323.2999999999956</v>
       </c>
       <c r="E83" s="17">
-        <f t="shared" si="12"/>
-        <v>53259.7</v>
-      </c>
-      <c r="F83" s="17">
-        <f t="shared" si="14"/>
-        <v>2323.2999999999956</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D83)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="5">
         <v>28</v>
       </c>
       <c r="B84" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1784.15</v>
       </c>
       <c r="C84" s="17">
-        <f t="shared" si="11"/>
-        <v>86589.7</v>
+        <f t="shared" si="7"/>
+        <v>68114.8</v>
       </c>
       <c r="D84" s="17">
-        <f t="shared" si="13"/>
-        <v>3830.3000000000029</v>
+        <f t="shared" si="8"/>
+        <v>2355.1000000000058</v>
       </c>
       <c r="E84" s="17">
-        <f t="shared" si="12"/>
-        <v>55614.8</v>
-      </c>
-      <c r="F84" s="17">
-        <f t="shared" si="14"/>
-        <v>2355.1000000000058</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D84)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="5">
         <v>29</v>
       </c>
       <c r="B85" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1870.9666666666667</v>
       </c>
       <c r="C85" s="17">
-        <f t="shared" si="11"/>
-        <v>90484.1</v>
+        <f t="shared" si="7"/>
+        <v>70502.100000000006</v>
       </c>
       <c r="D85" s="17">
-        <f t="shared" si="13"/>
-        <v>3894.4000000000087</v>
+        <f t="shared" si="8"/>
+        <v>2387.3000000000029</v>
       </c>
       <c r="E85" s="17">
-        <f t="shared" si="12"/>
-        <v>58002.1</v>
-      </c>
-      <c r="F85" s="17">
-        <f t="shared" si="14"/>
-        <v>2387.2999999999956</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f>MAX($D$56:D85)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="5">
         <v>30</v>
       </c>
       <c r="B86" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1959.6833333333334</v>
       </c>
       <c r="C86" s="17">
-        <f t="shared" si="11"/>
-        <v>94444.6</v>
+        <f t="shared" si="7"/>
+        <v>72922.3</v>
       </c>
       <c r="D86" s="17">
-        <f t="shared" si="13"/>
-        <v>3960.5</v>
+        <f t="shared" si="8"/>
+        <v>2420.1999999999971</v>
       </c>
       <c r="E86" s="17">
-        <f t="shared" si="12"/>
-        <v>60422.3</v>
-      </c>
-      <c r="F86" s="17">
-        <f t="shared" si="14"/>
-        <v>2420.2000000000044</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="30" t="s">
-        <v>141</v>
+        <f>MAX($D$56:D86)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="24" t="s">
+        <v>142</v>
       </c>
       <c r="D87" s="25">
-        <f>SUMPRODUCT(MAX((D56:D86&lt;=MES_PRICE)*A56:A86))</f>
+        <f>SUMPRODUCT((E56:E86&lt;=MES_PRICE)*1)-1</f>
         <v>6</v>
       </c>
-      <c r="F87" s="25">
-        <f>SUMPRODUCT(MAX((F56:F86&lt;=MES_PRICE)*A56:A86))</f>
-        <v>30</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A27"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A87"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A54:G54"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A52"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A54:G54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4270,7 +3974,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B1" s="13"/>
     </row>
@@ -4280,26 +3984,26 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4308,64 +4012,64 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B7" s="13"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4374,10 +4078,10 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4386,13 +4090,13 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B18" s="13"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B19" s="13">
         <v>10</v>
@@ -4400,7 +4104,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B20" s="13">
         <v>20</v>
@@ -4408,7 +4112,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B21" s="13">
         <v>30</v>
@@ -4416,10 +4120,10 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
